--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.19039902020359</v>
+        <v>9.130939840783084</v>
       </c>
       <c r="D2" t="n">
-        <v>56.86528330231796</v>
+        <v>9.240608536626668</v>
       </c>
       <c r="E2" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F2" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.56875709296469</v>
+        <v>8.542423027606763</v>
       </c>
       <c r="D3" t="n">
-        <v>53.04061251063184</v>
+        <v>8.619099532977675</v>
       </c>
       <c r="E3" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F3" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.18337365885863</v>
+        <v>9.454798219564529</v>
       </c>
       <c r="D4" t="n">
-        <v>58.40841268120647</v>
+        <v>9.491367060696051</v>
       </c>
       <c r="E4" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F4" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.62839657104222</v>
+        <v>8.877114442794362</v>
       </c>
       <c r="D5" t="n">
-        <v>55.27711845625853</v>
+        <v>8.982531749142012</v>
       </c>
       <c r="E5" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F5" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.86258342205132</v>
+        <v>4.852669806083339</v>
       </c>
       <c r="D6" t="n">
-        <v>30.15168073137587</v>
+        <v>4.899648118848579</v>
       </c>
       <c r="E6" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F6" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.89566185775374</v>
+        <v>9.083045051884982</v>
       </c>
       <c r="D7" t="n">
-        <v>56.23817259582838</v>
+        <v>9.138703046822112</v>
       </c>
       <c r="E7" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F7" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.42865463253511</v>
+        <v>7.219656377786956</v>
       </c>
       <c r="D8" t="n">
-        <v>44.37879124374696</v>
+        <v>7.211553577108881</v>
       </c>
       <c r="E8" t="n">
-        <v>9.290410223081603</v>
+        <v>1.50969166125076</v>
       </c>
       <c r="F8" t="n">
-        <v>9.386005076304794</v>
+        <v>1.525225824899529</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
